--- a/Data/Home/LivingRoom.Temperature.xlsx
+++ b/Data/Home/LivingRoom.Temperature.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H265"/>
+  <dimension ref="A1:I321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709236529</v>
+        <v>1711833615</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -501,6 +506,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709257647</v>
+        <v>1711846882</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,7 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +558,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709272106</v>
+        <v>1711850408</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -561,10 +568,11 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Warm</t>
+          <t>LivingRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +591,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709286718</v>
+        <v>1711856251</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -597,6 +605,7 @@
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +624,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709222633</v>
+        <v>1711874137</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -625,10 +634,11 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Cold</t>
+          <t>LivingRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +657,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709230379</v>
+        <v>1711888304</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -661,6 +671,7 @@
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +690,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709232465</v>
+        <v>1711893763</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -689,10 +700,11 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Cold</t>
+          <t>LivingRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -711,7 +723,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709237388</v>
+        <v>1711897337</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -725,6 +737,7 @@
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,7 +756,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709242536</v>
+        <v>1711916469</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -757,6 +770,7 @@
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,7 +789,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709245142</v>
+        <v>1711922875</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -789,6 +803,7 @@
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -807,7 +822,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709256805</v>
+        <v>1711926571</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -817,10 +832,11 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Warm</t>
+          <t>LivingRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -839,7 +855,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709276852</v>
+        <v>1711934016</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -853,6 +869,7 @@
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,7 +888,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709283241</v>
+        <v>1711939763</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -885,6 +902,7 @@
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -903,7 +921,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709310570</v>
+        <v>1711942611</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -917,6 +935,7 @@
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -935,7 +954,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709316011</v>
+        <v>1711952336</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -945,10 +964,11 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Cold</t>
+          <t>LivingRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -967,7 +987,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709323580</v>
+        <v>1711966760</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -977,10 +997,15 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Comfortable</t>
+          <t>LivingRoom.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -999,7 +1024,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709325695</v>
+        <v>1711969472</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1009,10 +1034,11 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Cold</t>
+          <t>LivingRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1031,7 +1057,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709329124</v>
+        <v>1711981332</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1045,6 +1071,7 @@
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1063,7 +1090,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709348530</v>
+        <v>1712002947</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1073,10 +1100,11 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Warm</t>
+          <t>LivingRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1095,7 +1123,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709365933</v>
+        <v>1712008872</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1109,6 +1137,7 @@
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1127,7 +1156,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709406124</v>
+        <v>1712012409</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1141,6 +1170,7 @@
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1159,7 +1189,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709410743</v>
+        <v>1712018529</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1173,6 +1203,7 @@
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1191,7 +1222,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709415858</v>
+        <v>1712021812</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1205,6 +1236,7 @@
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1223,7 +1255,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709418303</v>
+        <v>1712025780</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1237,6 +1269,7 @@
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1255,7 +1288,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709432726</v>
+        <v>1712039245</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1269,6 +1302,7 @@
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1287,7 +1321,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709443836</v>
+        <v>1712051239</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1301,6 +1335,11 @@
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1319,7 +1358,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709446014</v>
+        <v>1712054624</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1333,6 +1372,7 @@
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1351,7 +1391,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709454797</v>
+        <v>1712068237</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1365,6 +1405,7 @@
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1383,7 +1424,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709516215</v>
+        <v>1712088824</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1393,10 +1434,11 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Warm</t>
+          <t>LivingRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1415,7 +1457,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709528428</v>
+        <v>1712094759</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1425,10 +1467,11 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: ExcessivelyHot</t>
+          <t>LivingRoom.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1447,7 +1490,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709531915</v>
+        <v>1712098303</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1457,10 +1500,11 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Warm</t>
+          <t>LivingRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1479,7 +1523,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709541692</v>
+        <v>1712103689</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1493,6 +1537,7 @@
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1511,7 +1556,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709571641</v>
+        <v>1712107394</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1525,6 +1570,7 @@
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1543,7 +1589,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709576133</v>
+        <v>1712111520</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1557,6 +1603,7 @@
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1575,7 +1622,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709578264</v>
+        <v>1712123659</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1585,10 +1632,11 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Cold</t>
+          <t>LivingRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1607,7 +1655,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709581482</v>
+        <v>1712153551</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1621,6 +1669,7 @@
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1639,7 +1688,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1709605535</v>
+        <v>1712173404</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1649,10 +1698,11 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Warm</t>
+          <t>LivingRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1671,7 +1721,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1709610261</v>
+        <v>1712179440</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1681,10 +1731,11 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: ExcessivelyHot</t>
+          <t>LivingRoom.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1703,7 +1754,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1709614005</v>
+        <v>1712182914</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1713,10 +1764,11 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Warm</t>
+          <t>LivingRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1735,7 +1787,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1709625532</v>
+        <v>1712189270</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1749,6 +1801,7 @@
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1767,7 +1820,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1709634160</v>
+        <v>1712192605</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1781,6 +1834,7 @@
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1799,7 +1853,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1709636877</v>
+        <v>1712197486</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1813,6 +1867,7 @@
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1831,7 +1886,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1709660326</v>
+        <v>1712209937</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1841,10 +1896,11 @@
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Cold</t>
+          <t>LivingRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1863,7 +1919,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1709669528</v>
+        <v>1712224089</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1873,10 +1929,15 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Comfortable</t>
+          <t>LivingRoom.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1895,7 +1956,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1709676286</v>
+        <v>1712226638</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1905,10 +1966,11 @@
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Cold</t>
+          <t>LivingRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1927,7 +1989,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1709678471</v>
+        <v>1712237089</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1941,6 +2003,7 @@
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1959,7 +2022,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1709686275</v>
+        <v>1712261926</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1969,10 +2032,11 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Warm</t>
+          <t>LivingRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1991,7 +2055,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1709710632</v>
+        <v>1712267899</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2005,6 +2069,7 @@
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2023,7 +2088,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1709718534</v>
+        <v>1712271434</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2037,6 +2102,7 @@
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2055,7 +2121,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1709741231</v>
+        <v>1712276703</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2069,6 +2135,7 @@
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2087,7 +2154,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1709743204</v>
+        <v>1712279014</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2101,6 +2168,7 @@
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2119,7 +2187,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1709748747</v>
+        <v>1712283380</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2133,6 +2201,7 @@
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2151,7 +2220,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1709750419</v>
+        <v>1712288573</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2165,6 +2234,7 @@
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2183,7 +2253,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1709757467</v>
+        <v>1712289948</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2193,10 +2263,15 @@
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Comfortable</t>
+          <t>LivingRoom.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2215,7 +2290,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1709763668</v>
+        <v>1712291016</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2229,6 +2304,7 @@
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2247,7 +2323,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1709765240</v>
+        <v>1712292387</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2257,10 +2333,15 @@
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Comfortable</t>
+          <t>LivingRoom.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2279,7 +2360,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1709771170</v>
+        <v>1712293724</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2289,10 +2370,11 @@
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Warm</t>
+          <t>LivingRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2311,7 +2393,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1709786281</v>
+        <v>1712299263</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2321,10 +2403,11 @@
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: ExcessivelyHot</t>
+          <t>LivingRoom.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2343,7 +2426,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1709791123</v>
+        <v>1712302026</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2357,6 +2440,7 @@
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2375,7 +2459,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1709793884</v>
+        <v>1712327295</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2389,6 +2473,7 @@
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2407,7 +2492,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1709831632</v>
+        <v>1712354543</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2421,6 +2506,7 @@
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2439,7 +2525,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1709836212</v>
+        <v>1712360827</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2453,6 +2539,7 @@
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2471,7 +2558,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1709837798</v>
+        <v>1712364220</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2485,6 +2572,7 @@
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2503,7 +2591,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1709841531</v>
+        <v>1712366778</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2517,6 +2605,7 @@
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2535,7 +2624,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1709847093</v>
+        <v>1712368825</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2549,6 +2638,7 @@
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2567,7 +2657,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1709848693</v>
+        <v>1712373255</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2581,6 +2671,7 @@
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2599,7 +2690,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1709857421</v>
+        <v>1712390441</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2613,6 +2704,7 @@
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2631,7 +2723,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1709868252</v>
+        <v>1712397356</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2641,10 +2733,11 @@
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: ExcessivelyHot</t>
+          <t>LivingRoom.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2663,7 +2756,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1709872325</v>
+        <v>1712400977</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2677,6 +2770,7 @@
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2695,7 +2789,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1709881252</v>
+        <v>1712402813</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2705,10 +2799,15 @@
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Comfortable</t>
+          <t>LivingRoom.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2727,7 +2826,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1709886376</v>
+        <v>1712405167</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2737,10 +2836,11 @@
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Cold</t>
+          <t>LivingRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2759,7 +2859,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1709913818</v>
+        <v>1712411499</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2773,6 +2873,7 @@
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2791,7 +2892,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1709920451</v>
+        <v>1712434871</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2805,6 +2906,7 @@
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2823,7 +2925,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1709927459</v>
+        <v>1712441021</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2837,6 +2939,7 @@
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2855,7 +2958,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1709931488</v>
+        <v>1712444515</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2869,6 +2972,7 @@
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2887,7 +2991,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1709934070</v>
+        <v>1712450368</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2901,6 +3005,7 @@
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2919,7 +3024,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1709951689</v>
+        <v>1712452084</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2929,10 +3034,11 @@
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Warm</t>
+          <t>LivingRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2951,7 +3057,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1709973213</v>
+        <v>1712454844</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2965,6 +3071,7 @@
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2983,7 +3090,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1709980775</v>
+        <v>1712457691</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2997,6 +3104,7 @@
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3015,7 +3123,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1710002366</v>
+        <v>1712459714</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3029,6 +3137,7 @@
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3047,7 +3156,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1710004977</v>
+        <v>1712470260</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3057,10 +3166,11 @@
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Cold</t>
+          <t>LivingRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3079,7 +3189,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1710012647</v>
+        <v>1712481355</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3089,10 +3199,15 @@
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Comfortable</t>
+          <t>LivingRoom.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3111,7 +3226,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1710017754</v>
+        <v>1712484540</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3121,10 +3236,11 @@
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Cold</t>
+          <t>LivingRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3143,7 +3259,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1710020283</v>
+        <v>1712499731</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3157,6 +3273,7 @@
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3175,7 +3292,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1710033218</v>
+        <v>1712525065</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3185,10 +3302,11 @@
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Warm</t>
+          <t>LivingRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3207,7 +3325,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1710044103</v>
+        <v>1712531020</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3217,10 +3335,11 @@
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: ExcessivelyHot</t>
+          <t>LivingRoom.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3239,7 +3358,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1710047899</v>
+        <v>1712534596</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3249,10 +3368,11 @@
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Warm</t>
+          <t>LivingRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3271,7 +3391,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1710056312</v>
+        <v>1712544494</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3285,6 +3405,7 @@
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3303,7 +3424,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1710090809</v>
+        <v>1712549020</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3317,6 +3438,7 @@
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3335,7 +3457,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1710096778</v>
+        <v>1712549894</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3345,10 +3467,15 @@
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Comfortable</t>
+          <t>LivingRoom.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3367,7 +3494,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1710098791</v>
+        <v>1712552418</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3381,6 +3508,7 @@
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3399,7 +3527,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1710101449</v>
+        <v>1712555544</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3413,6 +3541,7 @@
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3431,7 +3560,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1710106633</v>
+        <v>1712563716</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3441,10 +3570,11 @@
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Cold</t>
+          <t>LivingRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3463,7 +3593,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1710109003</v>
+        <v>1712569273</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3477,6 +3607,7 @@
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3495,7 +3626,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1710121140</v>
+        <v>1712573123</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3509,6 +3640,7 @@
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3527,7 +3659,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1710132205</v>
+        <v>1712578144</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3537,10 +3669,11 @@
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: ExcessivelyHot</t>
+          <t>LivingRoom.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3559,7 +3692,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1710137513</v>
+        <v>1712607946</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3569,10 +3702,11 @@
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Warm</t>
+          <t>LivingRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3591,7 +3725,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1710144223</v>
+        <v>1712613971</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3605,6 +3739,7 @@
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3623,7 +3758,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1710183785</v>
+        <v>1712617440</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3637,6 +3772,7 @@
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3655,7 +3791,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1710190915</v>
+        <v>1712623207</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3669,6 +3805,7 @@
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3687,7 +3824,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1710195834</v>
+        <v>1712626244</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3701,6 +3838,7 @@
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3719,7 +3857,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1710198537</v>
+        <v>1712629848</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3733,6 +3871,7 @@
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3751,7 +3890,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1710215781</v>
+        <v>1712641714</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3765,6 +3904,7 @@
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3783,7 +3923,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1710227015</v>
+        <v>1712657626</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3793,10 +3933,15 @@
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Comfortable</t>
+          <t>LivingRoom.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3815,7 +3960,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1710231386</v>
+        <v>1712660374</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3829,6 +3974,7 @@
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3847,7 +3993,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1710233651</v>
+        <v>1712672253</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3861,6 +4007,7 @@
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3879,7 +4026,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1710267055</v>
+        <v>1712693774</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3893,6 +4040,7 @@
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3911,7 +4059,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1710271450</v>
+        <v>1712699657</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3925,6 +4073,7 @@
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3943,7 +4092,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1710276327</v>
+        <v>1712703179</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3957,6 +4106,7 @@
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3975,7 +4125,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1710278795</v>
+        <v>1712708556</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3989,6 +4139,7 @@
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4007,7 +4158,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1710294560</v>
+        <v>1712711592</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4017,10 +4168,11 @@
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Warm</t>
+          <t>LivingRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4039,7 +4191,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1710304927</v>
+        <v>1712715833</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4053,6 +4205,7 @@
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4071,7 +4224,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1710307758</v>
+        <v>1712730325</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4085,6 +4238,7 @@
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4103,7 +4257,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1710318562</v>
+        <v>1712743681</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4113,10 +4267,15 @@
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Comfortable</t>
+          <t>LivingRoom.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4135,7 +4294,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1710326156</v>
+        <v>1712746746</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4145,10 +4304,11 @@
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Cold</t>
+          <t>LivingRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4167,7 +4327,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1710330890</v>
+        <v>1712759474</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4181,6 +4341,7 @@
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4199,7 +4360,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1710334450</v>
+        <v>1712780650</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4213,6 +4374,7 @@
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4231,7 +4393,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1710346211</v>
+        <v>1712787114</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4245,6 +4407,7 @@
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4263,7 +4426,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1710349724</v>
+        <v>1712790599</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4277,6 +4440,7 @@
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4295,7 +4459,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1710357078</v>
+        <v>1712797376</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4309,6 +4473,7 @@
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4327,7 +4492,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1710360141</v>
+        <v>1712816344</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4337,10 +4502,11 @@
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Cold</t>
+          <t>LivingRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4359,7 +4525,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1710362730</v>
+        <v>1712830397</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4369,10 +4535,15 @@
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Comfortable</t>
+          <t>LivingRoom.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4391,7 +4562,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1710378949</v>
+        <v>1712832845</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4405,6 +4576,7 @@
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4423,7 +4595,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1710399724</v>
+        <v>1712853928</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4437,6 +4609,7 @@
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4455,7 +4628,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1710407739</v>
+        <v>1712867179</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4469,6 +4642,7 @@
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4487,7 +4661,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1710413663</v>
+        <v>1712873524</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4501,6 +4675,7 @@
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4519,7 +4694,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1710436159</v>
+        <v>1712877142</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4533,6 +4708,7 @@
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4551,7 +4727,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1710441798</v>
+        <v>1712883567</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4565,6 +4741,7 @@
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4583,7 +4760,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1710443826</v>
+        <v>1712889351</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4597,6 +4774,7 @@
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4615,7 +4793,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1710448793</v>
+        <v>1712891590</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4629,6 +4807,7 @@
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4647,7 +4826,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1710471283</v>
+        <v>1712894762</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4657,10 +4836,11 @@
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Warm</t>
+          <t>LivingRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4679,7 +4859,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1710480803</v>
+        <v>1712896097</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4689,10 +4869,15 @@
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: ExcessivelyHot</t>
+          <t>LivingRoom.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4711,7 +4896,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1710483690</v>
+        <v>1712897241</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4721,10 +4906,11 @@
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Warm</t>
+          <t>LivingRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4743,7 +4929,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1710491150</v>
+        <v>1712898592</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4753,10 +4939,15 @@
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Comfortable</t>
+          <t>LivingRoom.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4775,7 +4966,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1710526544</v>
+        <v>1712899784</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4789,6 +4980,7 @@
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4807,7 +4999,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1710532793</v>
+        <v>1712904656</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4821,6 +5013,7 @@
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4839,7 +5032,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1710534904</v>
+        <v>1712908877</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4849,10 +5042,11 @@
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Cold</t>
+          <t>LivingRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4871,7 +5065,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1710537407</v>
+        <v>1712930058</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4885,6 +5079,7 @@
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4903,7 +5098,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1710555068</v>
+        <v>1712959094</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4913,10 +5108,11 @@
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Warm</t>
+          <t>LivingRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4935,7 +5131,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1710564460</v>
+        <v>1712965363</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4949,6 +5145,7 @@
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4967,7 +5164,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1710566756</v>
+        <v>1712968921</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4977,10 +5174,11 @@
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Warm</t>
+          <t>LivingRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4999,7 +5197,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1710574167</v>
+        <v>1712971767</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -5013,6 +5211,7 @@
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5031,7 +5230,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1710615266</v>
+        <v>1712973899</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -5045,6 +5244,7 @@
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5063,7 +5263,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1710622750</v>
+        <v>1712977063</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -5077,6 +5277,7 @@
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5095,7 +5296,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1710641028</v>
+        <v>1712982618</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -5105,10 +5306,11 @@
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Warm</t>
+          <t>LivingRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5127,7 +5329,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1710646807</v>
+        <v>1712985736</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -5137,10 +5339,11 @@
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: ExcessivelyHot</t>
+          <t>LivingRoom.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5159,7 +5362,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1710649932</v>
+        <v>1712994067</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -5173,6 +5376,7 @@
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5191,7 +5395,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1710661944</v>
+        <v>1713001017</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -5205,6 +5409,7 @@
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5223,7 +5428,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1710666541</v>
+        <v>1713006709</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -5233,10 +5438,11 @@
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Cold</t>
+          <t>LivingRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5255,7 +5461,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1710670584</v>
+        <v>1713012020</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -5269,6 +5475,7 @@
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5287,7 +5494,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1710698235</v>
+        <v>1713018626</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -5297,10 +5504,11 @@
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Cold</t>
+          <t>LivingRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5319,7 +5527,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1710706011</v>
+        <v>1713024060</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -5333,6 +5541,7 @@
         </is>
       </c>
       <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5351,7 +5560,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1710713052</v>
+        <v>1713036903</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -5365,6 +5574,7 @@
         </is>
       </c>
       <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5383,7 +5593,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1710715772</v>
+        <v>1713042758</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -5397,6 +5607,7 @@
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5415,7 +5626,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1710727552</v>
+        <v>1713046364</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -5425,10 +5636,11 @@
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Warm</t>
+          <t>LivingRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5447,7 +5659,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1710736843</v>
+        <v>1713055879</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -5457,10 +5669,11 @@
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: ExcessivelyHot</t>
+          <t>LivingRoom.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5479,7 +5692,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1710742390</v>
+        <v>1713057770</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -5489,10 +5702,11 @@
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Warm</t>
+          <t>LivingRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5511,7 +5725,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1710752583</v>
+        <v>1713060125</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -5525,6 +5739,7 @@
         </is>
       </c>
       <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5543,7 +5758,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1710782934</v>
+        <v>1713071389</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -5553,10 +5768,11 @@
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Cold</t>
+          <t>LivingRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5575,7 +5791,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1710785250</v>
+        <v>1713106334</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -5589,6 +5805,7 @@
         </is>
       </c>
       <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5607,7 +5824,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1710787574</v>
+        <v>1713130508</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -5621,6 +5838,7 @@
         </is>
       </c>
       <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5639,7 +5857,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1710791939</v>
+        <v>1713136629</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -5653,6 +5871,7 @@
         </is>
       </c>
       <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5671,7 +5890,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1710795770</v>
+        <v>1713139891</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -5685,6 +5904,7 @@
         </is>
       </c>
       <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5703,7 +5923,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1710798039</v>
+        <v>1713144557</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -5717,6 +5937,7 @@
         </is>
       </c>
       <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5735,7 +5956,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1710813768</v>
+        <v>1713148157</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -5745,10 +5966,11 @@
       <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Warm</t>
+          <t>LivingRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5767,7 +5989,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1710821373</v>
+        <v>1713152032</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -5777,10 +5999,11 @@
       <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: ExcessivelyHot</t>
+          <t>LivingRoom.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5799,7 +6022,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1710824845</v>
+        <v>1713163466</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -5813,6 +6036,7 @@
         </is>
       </c>
       <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5831,7 +6055,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>1710835147</v>
+        <v>1713166629</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -5845,6 +6069,7 @@
         </is>
       </c>
       <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5863,7 +6088,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1710843878</v>
+        <v>1713168517</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -5873,10 +6098,11 @@
       <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Cold</t>
+          <t>LivingRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5895,7 +6121,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1710864881</v>
+        <v>1713176039</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -5909,6 +6135,7 @@
         </is>
       </c>
       <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5927,7 +6154,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1710870192</v>
+        <v>1713203862</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -5941,6 +6168,7 @@
         </is>
       </c>
       <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5959,7 +6187,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1710879180</v>
+        <v>1713208267</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5973,6 +6201,7 @@
         </is>
       </c>
       <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5991,7 +6220,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1710886326</v>
+        <v>1713240792</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -6001,10 +6230,11 @@
       <c r="F174" t="inlineStr"/>
       <c r="G174" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Cold</t>
+          <t>LivingRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6023,7 +6253,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1710888508</v>
+        <v>1713241759</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -6037,6 +6267,7 @@
         </is>
       </c>
       <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6055,7 +6286,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1710894023</v>
+        <v>1713242217</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -6065,10 +6296,11 @@
       <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Warm</t>
+          <t>LivingRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6087,7 +6319,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1710919141</v>
+        <v>1713243950</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -6101,6 +6333,7 @@
         </is>
       </c>
       <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6119,7 +6352,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1710926821</v>
+        <v>1713245436</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -6129,10 +6362,11 @@
       <c r="F178" t="inlineStr"/>
       <c r="G178" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Cold</t>
+          <t>LivingRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6151,7 +6385,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>1710929633</v>
+        <v>1713248490</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -6161,10 +6395,15 @@
       <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Comfortable</t>
+          <t>LivingRoom.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6183,7 +6422,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>1710933845</v>
+        <v>1713256004</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -6193,10 +6432,11 @@
       <c r="F180" t="inlineStr"/>
       <c r="G180" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Cold</t>
+          <t>LivingRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6215,7 +6455,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>1710951404</v>
+        <v>1713258499</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -6225,10 +6465,15 @@
       <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Comfortable</t>
+          <t>LivingRoom.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6247,7 +6492,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>1710956749</v>
+        <v>1713264067</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -6257,10 +6502,11 @@
       <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Cold</t>
+          <t>LivingRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6279,7 +6525,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>1710961641</v>
+        <v>1713280425</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -6293,6 +6539,7 @@
         </is>
       </c>
       <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -6311,7 +6558,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>1710963791</v>
+        <v>1713299049</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -6325,6 +6572,7 @@
         </is>
       </c>
       <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6343,7 +6591,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>1710967224</v>
+        <v>1713305048</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -6357,6 +6605,7 @@
         </is>
       </c>
       <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6375,7 +6624,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>1710972716</v>
+        <v>1713308625</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -6389,6 +6638,7 @@
         </is>
       </c>
       <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6407,7 +6657,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>1710974479</v>
+        <v>1713314270</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -6421,6 +6671,7 @@
         </is>
       </c>
       <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6439,7 +6690,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>1710982247</v>
+        <v>1713317965</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -6449,10 +6700,11 @@
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Warm</t>
+          <t>LivingRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6471,7 +6723,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>1711005677</v>
+        <v>1713321738</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -6485,6 +6737,7 @@
         </is>
       </c>
       <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6503,7 +6756,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>1711018117</v>
+        <v>1713327211</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -6517,6 +6770,7 @@
         </is>
       </c>
       <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6535,7 +6789,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>1711037409</v>
+        <v>1713330748</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -6549,6 +6803,7 @@
         </is>
       </c>
       <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6567,7 +6822,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>1711041129</v>
+        <v>1713334716</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -6577,10 +6832,11 @@
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Cold</t>
+          <t>LivingRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -6599,7 +6855,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>1711050967</v>
+        <v>1713339613</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -6609,10 +6865,15 @@
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Comfortable</t>
+          <t>LivingRoom.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -6631,7 +6892,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>1711056541</v>
+        <v>1713347417</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -6641,10 +6902,11 @@
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Cold</t>
+          <t>LivingRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -6663,7 +6925,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>1711058929</v>
+        <v>1713372515</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -6677,6 +6939,7 @@
         </is>
       </c>
       <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -6695,7 +6958,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>1711070773</v>
+        <v>1713390268</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -6705,10 +6968,11 @@
       <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Warm</t>
+          <t>LivingRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -6727,7 +6991,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>1711071932</v>
+        <v>1713396063</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -6741,6 +7005,7 @@
         </is>
       </c>
       <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -6759,7 +7024,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>1711072508</v>
+        <v>1713399462</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -6773,6 +7038,7 @@
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -6791,7 +7057,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>1711076458</v>
+        <v>1713410290</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -6801,10 +7067,11 @@
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: ExcessivelyCold</t>
+          <t>LivingRoom.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -6823,7 +7090,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>1711077894</v>
+        <v>1713411673</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -6837,6 +7104,7 @@
         </is>
       </c>
       <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -6855,7 +7123,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>1711080165</v>
+        <v>1713412638</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -6865,10 +7133,15 @@
       <c r="F201" t="inlineStr"/>
       <c r="G201" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Comfortable</t>
+          <t>LivingRoom.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -6887,7 +7160,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>1711082415</v>
+        <v>1713414240</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -6897,10 +7170,11 @@
       <c r="F202" t="inlineStr"/>
       <c r="G202" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Warm</t>
+          <t>LivingRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -6919,7 +7193,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>1711090701</v>
+        <v>1713415256</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -6929,10 +7203,15 @@
       <c r="F203" t="inlineStr"/>
       <c r="G203" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Comfortable</t>
+          <t>LivingRoom.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -6951,7 +7230,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>1711099594</v>
+        <v>1713416611</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -6965,6 +7244,7 @@
         </is>
       </c>
       <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -6983,7 +7263,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>1711141164</v>
+        <v>1713421546</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -6997,6 +7277,7 @@
         </is>
       </c>
       <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7015,7 +7296,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>1711149287</v>
+        <v>1713431048</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -7025,10 +7306,11 @@
       <c r="F206" t="inlineStr"/>
       <c r="G206" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Cold</t>
+          <t>LivingRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7047,7 +7329,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>1711151526</v>
+        <v>1713440080</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -7061,6 +7343,7 @@
         </is>
       </c>
       <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7079,7 +7362,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>1711158347</v>
+        <v>1713446969</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -7093,6 +7376,7 @@
         </is>
       </c>
       <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7111,7 +7395,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>1711174827</v>
+        <v>1713450556</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -7121,10 +7405,11 @@
       <c r="F209" t="inlineStr"/>
       <c r="G209" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: ExcessivelyHot</t>
+          <t>LivingRoom.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -7143,7 +7428,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>1711176542</v>
+        <v>1713470736</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -7153,10 +7438,11 @@
       <c r="F210" t="inlineStr"/>
       <c r="G210" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Warm</t>
+          <t>LivingRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -7175,7 +7461,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>1711180010</v>
+        <v>1713476870</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -7189,6 +7475,7 @@
         </is>
       </c>
       <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -7207,7 +7494,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>1711185843</v>
+        <v>1713480362</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -7221,6 +7508,7 @@
         </is>
       </c>
       <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -7239,7 +7527,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>1711191699</v>
+        <v>1713487239</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -7253,6 +7541,7 @@
         </is>
       </c>
       <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -7271,7 +7560,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>1711215088</v>
+        <v>1713490856</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -7285,6 +7574,7 @@
         </is>
       </c>
       <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -7303,7 +7593,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>1711222157</v>
+        <v>1713494751</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -7317,6 +7607,7 @@
         </is>
       </c>
       <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -7335,7 +7626,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>1711224266</v>
+        <v>1713507024</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -7345,10 +7636,11 @@
       <c r="F216" t="inlineStr"/>
       <c r="G216" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Cold</t>
+          <t>LivingRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -7367,7 +7659,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>1711227085</v>
+        <v>1713514851</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -7377,10 +7669,15 @@
       <c r="F217" t="inlineStr"/>
       <c r="G217" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Comfortable</t>
+          <t>LivingRoom.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -7399,7 +7696,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>1711247839</v>
+        <v>1713522282</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -7413,6 +7710,7 @@
         </is>
       </c>
       <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -7431,7 +7729,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>1711266237</v>
+        <v>1713535824</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -7441,10 +7739,11 @@
       <c r="F219" t="inlineStr"/>
       <c r="G219" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: ExcessivelyHot</t>
+          <t>LivingRoom.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -7463,7 +7762,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>1711268458</v>
+        <v>1713558808</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -7473,10 +7772,11 @@
       <c r="F220" t="inlineStr"/>
       <c r="G220" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Warm</t>
+          <t>LivingRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -7495,7 +7795,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>1711272869</v>
+        <v>1713564811</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -7509,6 +7809,7 @@
         </is>
       </c>
       <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -7527,7 +7828,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>1711297382</v>
+        <v>1713568299</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -7541,6 +7842,7 @@
         </is>
       </c>
       <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -7559,7 +7861,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>1711299467</v>
+        <v>1713574060</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -7573,6 +7875,7 @@
         </is>
       </c>
       <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -7591,7 +7894,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>1711303024</v>
+        <v>1713575706</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -7605,6 +7908,7 @@
         </is>
       </c>
       <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -7623,7 +7927,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>1711310560</v>
+        <v>1713578942</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -7637,6 +7941,7 @@
         </is>
       </c>
       <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -7655,7 +7960,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>1711315775</v>
+        <v>1713582258</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -7669,6 +7974,7 @@
         </is>
       </c>
       <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -7687,7 +7993,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>1711318393</v>
+        <v>1713585766</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -7701,6 +8007,7 @@
         </is>
       </c>
       <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -7719,7 +8026,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>1711332712</v>
+        <v>1713593108</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -7733,6 +8040,7 @@
         </is>
       </c>
       <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -7751,7 +8059,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>1711343354</v>
+        <v>1713611115</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -7765,6 +8073,11 @@
         </is>
       </c>
       <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -7783,7 +8096,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>1711346676</v>
+        <v>1713613637</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -7797,6 +8110,7 @@
         </is>
       </c>
       <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -7815,7 +8129,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>1711358613</v>
+        <v>1713615305</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -7825,10 +8139,15 @@
       <c r="F231" t="inlineStr"/>
       <c r="G231" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Comfortable</t>
+          <t>LivingRoom.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -7847,7 +8166,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>1711362311</v>
+        <v>1713617723</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -7857,10 +8176,11 @@
       <c r="F232" t="inlineStr"/>
       <c r="G232" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Cold</t>
+          <t>LivingRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -7879,7 +8199,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>1711363786</v>
+        <v>1713625621</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -7893,6 +8213,7 @@
         </is>
       </c>
       <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -7911,7 +8232,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>1711388216</v>
+        <v>1713637605</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -7925,6 +8246,7 @@
         </is>
       </c>
       <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -7943,7 +8265,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>1711392053</v>
+        <v>1713643051</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -7957,6 +8279,7 @@
         </is>
       </c>
       <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -7975,7 +8298,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>1711394487</v>
+        <v>1713644846</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -7989,6 +8312,7 @@
         </is>
       </c>
       <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -8007,7 +8331,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>1711396177</v>
+        <v>1713659401</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -8021,6 +8345,7 @@
         </is>
       </c>
       <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -8039,7 +8364,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>1711424952</v>
+        <v>1713660810</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
@@ -8049,10 +8374,11 @@
       <c r="F238" t="inlineStr"/>
       <c r="G238" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Warm</t>
+          <t>LivingRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H238" t="inlineStr"/>
+      <c r="I238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -8071,7 +8397,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>1711438570</v>
+        <v>1713662835</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
@@ -8081,10 +8407,11 @@
       <c r="F239" t="inlineStr"/>
       <c r="G239" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: ExcessivelyHot</t>
+          <t>LivingRoom.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H239" t="inlineStr"/>
+      <c r="I239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -8103,7 +8430,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>1711443695</v>
+        <v>1713670912</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
@@ -8117,6 +8444,7 @@
         </is>
       </c>
       <c r="H240" t="inlineStr"/>
+      <c r="I240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -8135,7 +8463,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>1711453914</v>
+        <v>1713681452</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -8145,10 +8473,15 @@
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Comfortable</t>
+          <t>LivingRoom.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -8167,7 +8500,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>1711463754</v>
+        <v>1713685253</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
@@ -8177,10 +8510,11 @@
       <c r="F242" t="inlineStr"/>
       <c r="G242" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Cold</t>
+          <t>LivingRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -8199,7 +8533,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>1711465562</v>
+        <v>1713687754</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -8209,10 +8543,15 @@
       <c r="F243" t="inlineStr"/>
       <c r="G243" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Comfortable</t>
+          <t>LivingRoom.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -8231,7 +8570,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>1711474664</v>
+        <v>1713691222</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -8241,10 +8580,11 @@
       <c r="F244" t="inlineStr"/>
       <c r="G244" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Cold</t>
+          <t>LivingRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H244" t="inlineStr"/>
+      <c r="I244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -8263,7 +8603,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>1711479102</v>
+        <v>1713702443</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -8277,6 +8617,7 @@
         </is>
       </c>
       <c r="H245" t="inlineStr"/>
+      <c r="I245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -8295,7 +8636,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>1711482083</v>
+        <v>1713724053</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -8309,6 +8650,7 @@
         </is>
       </c>
       <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -8327,7 +8669,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>1711483782</v>
+        <v>1713729550</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -8341,6 +8683,7 @@
         </is>
       </c>
       <c r="H247" t="inlineStr"/>
+      <c r="I247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -8359,7 +8702,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>1711511100</v>
+        <v>1713731429</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -8369,10 +8712,11 @@
       <c r="F248" t="inlineStr"/>
       <c r="G248" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Warm</t>
+          <t>LivingRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H248" t="inlineStr"/>
+      <c r="I248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -8391,7 +8735,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>1711515460</v>
+        <v>1713743746</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -8405,6 +8749,7 @@
         </is>
       </c>
       <c r="H249" t="inlineStr"/>
+      <c r="I249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -8423,7 +8768,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>1711523730</v>
+        <v>1713745406</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -8433,10 +8778,11 @@
       <c r="F250" t="inlineStr"/>
       <c r="G250" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Warm</t>
+          <t>LivingRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H250" t="inlineStr"/>
+      <c r="I250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -8455,7 +8801,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>1711534239</v>
+        <v>1713749457</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
@@ -8469,6 +8815,7 @@
         </is>
       </c>
       <c r="H251" t="inlineStr"/>
+      <c r="I251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -8487,7 +8834,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>1711548008</v>
+        <v>1713757196</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
@@ -8497,10 +8844,11 @@
       <c r="F252" t="inlineStr"/>
       <c r="G252" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Cold</t>
+          <t>LivingRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H252" t="inlineStr"/>
+      <c r="I252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -8519,7 +8867,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>1711552666</v>
+        <v>1713770790</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
@@ -8529,10 +8877,15 @@
       <c r="F253" t="inlineStr"/>
       <c r="G253" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Comfortable</t>
+          <t>LivingRoom.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H253" t="inlineStr"/>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -8551,7 +8904,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>1711555681</v>
+        <v>1713778173</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
@@ -8561,10 +8914,11 @@
       <c r="F254" t="inlineStr"/>
       <c r="G254" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Cold</t>
+          <t>LivingRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H254" t="inlineStr"/>
+      <c r="I254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -8583,7 +8937,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>1711557044</v>
+        <v>1713792391</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
@@ -8597,6 +8951,7 @@
         </is>
       </c>
       <c r="H255" t="inlineStr"/>
+      <c r="I255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -8615,7 +8970,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>1711561540</v>
+        <v>1713816734</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -8629,6 +8984,7 @@
         </is>
       </c>
       <c r="H256" t="inlineStr"/>
+      <c r="I256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -8647,7 +9003,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>1711565999</v>
+        <v>1713823148</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
@@ -8661,6 +9017,7 @@
         </is>
       </c>
       <c r="H257" t="inlineStr"/>
+      <c r="I257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -8679,7 +9036,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>1711568594</v>
+        <v>1713826761</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
@@ -8693,6 +9050,7 @@
         </is>
       </c>
       <c r="H258" t="inlineStr"/>
+      <c r="I258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -8711,7 +9069,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>1711570300</v>
+        <v>1713832712</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
@@ -8725,6 +9083,7 @@
         </is>
       </c>
       <c r="H259" t="inlineStr"/>
+      <c r="I259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -8743,7 +9102,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>1711594911</v>
+        <v>1713837009</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
@@ -8753,10 +9112,11 @@
       <c r="F260" t="inlineStr"/>
       <c r="G260" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Warm</t>
+          <t>LivingRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H260" t="inlineStr"/>
+      <c r="I260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -8775,7 +9135,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>1711601450</v>
+        <v>1713840493</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
@@ -8789,6 +9149,7 @@
         </is>
       </c>
       <c r="H261" t="inlineStr"/>
+      <c r="I261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -8807,7 +9168,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>1711609270</v>
+        <v>1713850379</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
@@ -8821,6 +9182,7 @@
         </is>
       </c>
       <c r="H262" t="inlineStr"/>
+      <c r="I262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -8839,7 +9201,7 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>1711620125</v>
+        <v>1713858685</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
@@ -8849,10 +9211,15 @@
       <c r="F263" t="inlineStr"/>
       <c r="G263" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Comfortable</t>
+          <t>LivingRoom.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H263" t="inlineStr"/>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -8871,7 +9238,7 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>1711634936</v>
+        <v>1713860937</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
@@ -8881,10 +9248,11 @@
       <c r="F264" t="inlineStr"/>
       <c r="G264" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Cold</t>
+          <t>LivingRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H264" t="inlineStr"/>
+      <c r="I264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -8903,7 +9271,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>1711637539</v>
+        <v>1713863768</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
@@ -8913,10 +9281,1875 @@
       <c r="F265" t="inlineStr"/>
       <c r="G265" t="inlineStr">
         <is>
-          <t>LivingRoom.Temperature.state: Comfortable</t>
+          <t>LivingRoom.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H265" t="inlineStr"/>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D266" t="n">
+        <v>1713865903</v>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr"/>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Warm</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr"/>
+      <c r="I266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D267" t="n">
+        <v>1713881513</v>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr"/>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr"/>
+      <c r="I267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D268" t="n">
+        <v>1713907918</v>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr"/>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Cold</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr"/>
+      <c r="I268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D269" t="n">
+        <v>1713913977</v>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr"/>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr"/>
+      <c r="I269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D270" t="n">
+        <v>1713917359</v>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr"/>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Cold</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr"/>
+      <c r="I270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D271" t="n">
+        <v>1713921977</v>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr"/>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr"/>
+      <c r="I271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D272" t="n">
+        <v>1713925527</v>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr"/>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Cold</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr"/>
+      <c r="I272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D273" t="n">
+        <v>1713929436</v>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr"/>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr"/>
+      <c r="I273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D274" t="n">
+        <v>1713938678</v>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr"/>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Warm</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr"/>
+      <c r="I274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D275" t="n">
+        <v>1713948617</v>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr"/>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr"/>
+      <c r="I275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D276" t="n">
+        <v>1713952264</v>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr"/>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Warm</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr"/>
+      <c r="I276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D277" t="n">
+        <v>1713959969</v>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr"/>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr"/>
+      <c r="I277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D278" t="n">
+        <v>1713994365</v>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr"/>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Cold</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr"/>
+      <c r="I278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D279" t="n">
+        <v>1714000359</v>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr"/>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr"/>
+      <c r="I279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D280" t="n">
+        <v>1714004087</v>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr"/>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Cold</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr"/>
+      <c r="I280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D281" t="n">
+        <v>1714014124</v>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr"/>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr"/>
+      <c r="I281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D282" t="n">
+        <v>1714027888</v>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr"/>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Warm</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr"/>
+      <c r="I282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D283" t="n">
+        <v>1714032437</v>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr"/>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr"/>
+      <c r="I283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D284" t="n">
+        <v>1714035505</v>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr"/>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Warm</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr"/>
+      <c r="I284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D285" t="n">
+        <v>1714041395</v>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr"/>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr"/>
+      <c r="I285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D286" t="n">
+        <v>1714045723</v>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr"/>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Warm</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr"/>
+      <c r="I286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D287" t="n">
+        <v>1714049548</v>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr"/>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr"/>
+      <c r="I287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D288" t="n">
+        <v>1714075826</v>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr"/>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Cold</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr"/>
+      <c r="I288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D289" t="n">
+        <v>1714082194</v>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr"/>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr"/>
+      <c r="I289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D290" t="n">
+        <v>1714085788</v>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr"/>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Cold</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr"/>
+      <c r="I290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D291" t="n">
+        <v>1714091490</v>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr"/>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr"/>
+      <c r="I291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D292" t="n">
+        <v>1714094948</v>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr"/>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Cold</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr"/>
+      <c r="I292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D293" t="n">
+        <v>1714098734</v>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr"/>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr"/>
+      <c r="I293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D294" t="n">
+        <v>1714103899</v>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr"/>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Cold</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr"/>
+      <c r="I294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D295" t="n">
+        <v>1714106929</v>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr"/>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr"/>
+      <c r="I295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D296" t="n">
+        <v>1714114016</v>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr"/>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Warm</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr"/>
+      <c r="I296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D297" t="n">
+        <v>1714128131</v>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr"/>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: ExcessivelyHot</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr"/>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D298" t="n">
+        <v>1714130536</v>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr"/>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Warm</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr"/>
+      <c r="I298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D299" t="n">
+        <v>1714141384</v>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr"/>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr"/>
+      <c r="I299" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D300" t="n">
+        <v>1714162260</v>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr"/>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Cold</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr"/>
+      <c r="I300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D301" t="n">
+        <v>1714168544</v>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr"/>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr"/>
+      <c r="I301" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D302" t="n">
+        <v>1714172098</v>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr"/>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Cold</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr"/>
+      <c r="I302" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D303" t="n">
+        <v>1714178250</v>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr"/>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr"/>
+      <c r="I303" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D304" t="n">
+        <v>1714180009</v>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr"/>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Cold</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr"/>
+      <c r="I304" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D305" t="n">
+        <v>1714182944</v>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr"/>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr"/>
+      <c r="I305" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D306" t="n">
+        <v>1714197737</v>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr"/>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Warm</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr"/>
+      <c r="I306" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D307" t="n">
+        <v>1714213034</v>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr"/>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: ExcessivelyHot</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr"/>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D308" t="n">
+        <v>1714218596</v>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr"/>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Warm</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr"/>
+      <c r="I308" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D309" t="n">
+        <v>1714228234</v>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr"/>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr"/>
+      <c r="I309" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D310" t="n">
+        <v>1714249738</v>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr"/>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Cold</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr"/>
+      <c r="I310" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D311" t="n">
+        <v>1714255820</v>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr"/>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr"/>
+      <c r="I311" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D312" t="n">
+        <v>1714259296</v>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr"/>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Cold</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr"/>
+      <c r="I312" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D313" t="n">
+        <v>1714265455</v>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr"/>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr"/>
+      <c r="I313" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D314" t="n">
+        <v>1714267034</v>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr"/>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Cold</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr"/>
+      <c r="I314" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D315" t="n">
+        <v>1714270006</v>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr"/>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr"/>
+      <c r="I315" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D316" t="n">
+        <v>1714272892</v>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr"/>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Cold</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr"/>
+      <c r="I316" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D317" t="n">
+        <v>1714274988</v>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr"/>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr"/>
+      <c r="I317" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D318" t="n">
+        <v>1714284425</v>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr"/>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Warm</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr"/>
+      <c r="I318" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D319" t="n">
+        <v>1714298209</v>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr"/>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: ExcessivelyHot</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr"/>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D320" t="n">
+        <v>1714303972</v>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr"/>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Warm</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr"/>
+      <c r="I320" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D321" t="n">
+        <v>1714316490</v>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr"/>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>LivingRoom.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr"/>
+      <c r="I321" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
